--- a/courses/product_section/guide/module_1/module1_practice.xlsx
+++ b/courses/product_section/guide/module_1/module1_practice.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Маркетплейс" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. SaaS-подписка" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. EdTech — когорты" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1. Маркетплейс" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. SaaS-подписка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. EdTech — когорты" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,7 +51,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -88,8 +88,14 @@
         <fgColor rgb="00EBEBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -125,11 +131,99 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001F4E79"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001F4E79"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F4E79"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001F4E79"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001F4E79"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F4E79"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,6 +283,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -568,6 +676,8 @@
           <t>Лист 1 — Маркетплейс одежды</t>
         </is>
       </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="22" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -579,7 +689,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>🟡 Жёлтые ячейки — заполни формулой.  ✅ Зелёные — итоговые выводы.</t>
+          <t>🟡 Жёлтые ячейки — заполни формулой или числом.  ✅ Зелёные — итоговые выводы.</t>
         </is>
       </c>
     </row>
@@ -589,6 +699,8 @@
           <t>ИСХОДНЫЕ ДАННЫЕ</t>
         </is>
       </c>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="24" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -651,6 +763,8 @@
           <t>РАССЧИТАЙ МЕТРИКИ</t>
         </is>
       </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="24" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -675,9 +789,10 @@
           <t>Take Rate, %</t>
         </is>
       </c>
-      <c r="B12" s="9">
-        <f>Revenue/GMV*100</f>
-        <v/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Revenue ÷ GMV × 100</t>
+        </is>
       </c>
       <c r="C12" s="10" t="n"/>
     </row>
@@ -687,9 +802,10 @@
           <t>AOV (средний чек), ₽</t>
         </is>
       </c>
-      <c r="B13" s="9">
-        <f>GMV/Заказов</f>
-        <v/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>GMV ÷ Количество заказов</t>
+        </is>
       </c>
       <c r="C13" s="10" t="n"/>
     </row>
@@ -699,9 +815,10 @@
           <t>ARPU, ₽</t>
         </is>
       </c>
-      <c r="B14" s="9">
-        <f>Revenue/MAU</f>
-        <v/>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Revenue ÷ MAU</t>
+        </is>
       </c>
       <c r="C14" s="10" t="n"/>
     </row>
@@ -711,9 +828,10 @@
           <t>ARPPU, ₽</t>
         </is>
       </c>
-      <c r="B15" s="9">
-        <f>Revenue/Платящих</f>
-        <v/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Revenue ÷ Платящих</t>
+        </is>
       </c>
       <c r="C15" s="10" t="n"/>
     </row>
@@ -723,9 +841,10 @@
           <t>Доля платящих пользователей, %</t>
         </is>
       </c>
-      <c r="B16" s="9">
-        <f>Платящих/MAU*100</f>
-        <v/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Платящих ÷ MAU × 100</t>
+        </is>
       </c>
       <c r="C16" s="10" t="n"/>
     </row>
@@ -735,9 +854,10 @@
           <t>Заказов на платящего в месяц</t>
         </is>
       </c>
-      <c r="B17" s="9">
-        <f>Заказов/Платящих</f>
-        <v/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Заказов ÷ Платящих</t>
+        </is>
       </c>
       <c r="C17" s="10" t="n"/>
     </row>
@@ -747,6 +867,8 @@
           <t>ВОПРОС ДЛЯ АНАЛИЗА</t>
         </is>
       </c>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="24" t="n"/>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -754,24 +876,28 @@
           <t>GMV вырос на 15% в следующем месяце, Revenue — на 8%. Что могло произойти? Назови две гипотезы.</t>
         </is>
       </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="24" t="n"/>
     </row>
     <row r="21" ht="50" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Твой ответ:</t>
         </is>
       </c>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -798,6 +924,8 @@
           <t>Лист 2 — SaaS-подписка (B2B)</t>
         </is>
       </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="22" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -809,7 +937,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>🟡 Жёлтые ячейки — заполни формулой.  ✅ Зелёные — итоговые выводы.</t>
+          <t>🟡 Жёлтые ячейки — заполни формулой или числом.  ✅ Зелёные — итоговые выводы.</t>
         </is>
       </c>
     </row>
@@ -819,6 +947,8 @@
           <t>ИСХОДНЫЕ ДАННЫЕ</t>
         </is>
       </c>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="24" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -856,11 +986,11 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Churn Rate, % в месяц</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>3</v>
+          <t>Churn Rate, в месяц</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>0.03</v>
       </c>
       <c r="C8" s="7" t="n"/>
     </row>
@@ -870,6 +1000,8 @@
           <t>РАССЧИТАЙ МЕТРИКИ</t>
         </is>
       </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="24" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -959,6 +1091,8 @@
           <t>ТАБЛИЦА ЧУВСТВИТЕЛЬНОСТИ — как churn влияет на LTV</t>
         </is>
       </c>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="24" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -983,40 +1117,32 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>0.01</v>
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
+      <c r="A21" s="18" t="n">
+        <v>0.03</v>
       </c>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
+      <c r="A22" s="18" t="n">
+        <v>0.05</v>
       </c>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="10" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="A23" s="18" t="n">
+        <v>0.1</v>
       </c>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
@@ -1028,6 +1154,9 @@
           <t>ВОПРОС ДЛЯ АНАЛИЗА</t>
         </is>
       </c>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -1035,25 +1164,31 @@
           <t>При каком churn unit-экономика перестаёт быть устойчивой (LTV/CAC &lt; 3)? Что это значит для продукта?</t>
         </is>
       </c>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
     </row>
     <row r="27" ht="50" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>Твой ответ:</t>
         </is>
       </c>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1065,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1085,6 +1220,14 @@
           <t>Лист 3 — EdTech-платформа: когортный анализ</t>
         </is>
       </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="21" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="22" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -1096,7 +1239,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>🟡 Жёлтые ячейки — заполни.  Часть B: посчитай абсолютные числа (размер × retention%).</t>
+          <t>🟡 Жёлтые ячейки — заполни.  ✅ Зелёные — итоговые выводы.</t>
         </is>
       </c>
     </row>
@@ -1106,6 +1249,14 @@
           <t>ЧАСТЬ А — Retention % (дано)</t>
         </is>
       </c>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="23" t="n"/>
+      <c r="D4" s="23" t="n"/>
+      <c r="E4" s="23" t="n"/>
+      <c r="F4" s="23" t="n"/>
+      <c r="G4" s="23" t="n"/>
+      <c r="H4" s="23" t="n"/>
+      <c r="I4" s="24" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -1353,6 +1504,14 @@
           <t>ЧАСТЬ Б — Абсолютное число активных (посчитай сам: Размер × Retention%)</t>
         </is>
       </c>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="24" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1558,6 +1717,14 @@
           <t>ЧАСТЬ В — Анализ</t>
         </is>
       </c>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="24" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
@@ -1565,43 +1732,81 @@
           <t>1. Посчитай M3 retention для каждой когорты где он есть. Есть ли тренд?</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="23" t="n"/>
+      <c r="I23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>Твой ответ:</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>2. Посчитай среднее M1 retention по всем когортам.</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Твой ответ:</t>
-        </is>
-      </c>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="n"/>
+      <c r="I24" s="24" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>3. Retention растёт от когорты к когорте. Какие три гипотезы объясняют рост?</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Твой ответ:</t>
-        </is>
-      </c>
+      <c r="A25" s="20" t="n"/>
+      <c r="E25" s="27" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
+          <t>2. Посчитай среднее M1 retention по всем когортам.</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Твой ответ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3. Retention растёт от когорты к когорте. Какие три гипотезы объясняют рост?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Твой ответ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>4. Июньская когорта самая большая (680 студентов). Что могло привлечь больше студентов?</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Твой ответ:</t>
         </is>
@@ -1609,20 +1814,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:I23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:I25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:I26"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:H11">
     <cfRule type="colorScale" priority="1">
